--- a/resources/templates/standard/B1100-11.xlsx
+++ b/resources/templates/standard/B1100-11.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>부적합 보관장 관리 대장</t>
   </si>
@@ -706,12 +709,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="20.1" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -844,42 +849,42 @@
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
       <c r="E4" s="5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
       <c r="H4" s="6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
       <c r="L4" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
       <c r="P4" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q4" s="4"/>
       <c r="R4" s="4"/>
       <c r="S4" s="4"/>
       <c r="T4" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U4" s="5"/>
       <c r="V4" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W4" s="4"/>
       <c r="X4" s="4"/>
@@ -887,7 +892,7 @@
       <c r="Z4" s="4"/>
       <c r="AA4" s="4"/>
       <c r="AB4" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC4" s="7"/>
       <c r="AD4" s="7"/>
@@ -903,7 +908,7 @@
       <c r="AN4" s="7"/>
       <c r="AO4" s="7"/>
       <c r="AP4" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ4" s="6"/>
     </row>
@@ -936,28 +941,28 @@
       <c r="Z5" s="4"/>
       <c r="AA5" s="4"/>
       <c r="AB5" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AC5" s="8"/>
       <c r="AD5" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AE5" s="9"/>
       <c r="AF5" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG5" s="9"/>
       <c r="AH5" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI5" s="9"/>
       <c r="AJ5" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK5" s="9"/>
       <c r="AL5" s="9"/>
       <c r="AM5" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AN5" s="9"/>
       <c r="AO5" s="9"/>
@@ -1776,7 +1781,7 @@
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A24" s="18" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B24" s="18"/>
       <c r="C24" s="18"/>
